--- a/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="11_07EE13C193757A3225BDE5FB35085310783B1F5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0930A784-61FA-4E16-94ED-682FF0A5A588}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="11_07EE13C193757A3225BDE5FB35085310783B1F5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDDA5559-B9D5-4500-86F1-F943223E206D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="100">
   <si>
     <t>Project ID</t>
   </si>
@@ -128,13 +131,13 @@
     <t>Renewable Energy</t>
   </si>
   <si>
+    <t>Percent share of RE in the power generation mix of the Philippines – based on installed capacity.</t>
+  </si>
+  <si>
+    <t>Reported progress is based on Philippine government data on annual generation mix</t>
+  </si>
+  <si>
     <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Percent share of RE in the power generation mix of the Philippines – based on installed capacity.</t>
-  </si>
-  <si>
-    <t>Reported progress is based on Philippine government data on annual generation mix</t>
   </si>
   <si>
     <t>Number of sitio households in far-flung areas that have obtained access to reliable sources of renewable energy due to the Project</t>
@@ -549,18 +552,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -603,6 +594,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,34 +922,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="5" customFormat="1">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="12" t="s">
@@ -978,579 +981,577 @@
       </c>
     </row>
     <row r="2" spans="1:19" s="5" customFormat="1">
-      <c r="A2" s="23">
+      <c r="A2" s="19">
         <v>5304</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="19">
         <v>2639726</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24">
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20">
         <v>222</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="26" t="s">
+      <c r="I2" s="21"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
     </row>
     <row r="3" spans="1:19" s="5" customFormat="1" ht="30.75">
-      <c r="A3" s="23">
+      <c r="A3" s="19">
         <v>5194</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="19">
         <v>5200000</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="24">
-        <v>0</v>
-      </c>
-      <c r="H3" s="24">
+      <c r="G3" s="20">
+        <v>0</v>
+      </c>
+      <c r="H3" s="20">
         <v>205000</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20" t="s">
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="19"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
     </row>
     <row r="4" spans="1:19" s="5" customFormat="1" ht="30.75">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="G4" s="24">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.35</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="28">
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="H4" s="29">
-        <v>0.35</v>
-      </c>
-      <c r="I4" s="27" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="26"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+    </row>
+    <row r="5" spans="1:19" s="5" customFormat="1" ht="54.75">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="30"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-    </row>
-    <row r="5" spans="1:19" s="5" customFormat="1" ht="54.75">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="23">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23" t="s">
+      <c r="G5" s="19">
+        <v>0</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="31" t="s">
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-    </row>
-    <row r="6" spans="1:19" s="5" customFormat="1" ht="409.6">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32" t="s">
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+    </row>
+    <row r="6" spans="1:19" s="5" customFormat="1" ht="238.5" customHeight="1">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="32">
-        <v>0</v>
-      </c>
-      <c r="H6" s="32">
+      <c r="G6" s="28">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28">
         <v>8</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="34" t="s">
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
     </row>
     <row r="7" spans="1:19" s="5" customFormat="1" ht="30.75">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="23">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="G7" s="19">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
         <v>12</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="I7" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="19">
         <v>9</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="19">
         <v>50</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="I8" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
     </row>
     <row r="9" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="23">
-        <v>0</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="27" t="s">
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="26"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
     </row>
     <row r="10" spans="1:19" s="5" customFormat="1" ht="60.75">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="23">
-        <v>0</v>
-      </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="27" t="s">
+      <c r="G10" s="19">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="26"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="23">
-        <v>0</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="27" t="s">
+      <c r="G11" s="19">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="30"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="26"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
     </row>
     <row r="12" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="23">
-        <v>0</v>
-      </c>
-      <c r="H12" s="23">
+      <c r="G12" s="19">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
         <v>10</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="I12" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
     </row>
     <row r="13" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="23">
-        <v>0</v>
-      </c>
-      <c r="H13" s="23">
+      <c r="G13" s="19">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19">
         <v>15</v>
       </c>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
     </row>
     <row r="14" spans="1:19" s="5" customFormat="1" ht="30.75">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="23">
-        <v>0</v>
-      </c>
-      <c r="H14" s="22">
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
         <v>15</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="I14" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="76.5">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="23">
-        <v>0</v>
-      </c>
-      <c r="H15" s="23">
+      <c r="G15" s="19">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19">
         <v>3</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="I15" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="45.75">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="23">
-        <v>0</v>
-      </c>
-      <c r="H16" s="23">
+      <c r="G16" s="19">
+        <v>0</v>
+      </c>
+      <c r="H16" s="19">
         <v>10</v>
       </c>
-      <c r="I16" s="27" t="s">
+      <c r="I16" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
     </row>
     <row r="17" spans="1:19" s="5" customFormat="1" ht="137.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="23">
-        <v>0</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
         <v>5</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
     </row>
     <row r="18" spans="1:19" s="5" customFormat="1" ht="121.5">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="23">
-        <v>0</v>
-      </c>
-      <c r="H18" s="22">
+      <c r="G18" s="19">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
         <v>75</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -1705,10 +1706,10 @@
     </row>
     <row r="4" spans="1:13" s="5" customFormat="1" ht="30.75">
       <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="G4" s="9">
         <v>0.14399999999999999</v>
@@ -1717,7 +1718,7 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>22</v>
@@ -1726,7 +1727,7 @@
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="45.75">
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>33</v>
@@ -2133,7 +2134,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="9">
         <v>0.14399999999999999</v>
@@ -2142,7 +2143,7 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="45.75">
@@ -2156,7 +2157,7 @@
         <v>5200000</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>33</v>
@@ -2547,18 +2548,18 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="32" t="s">
         <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="16"/>
+      <c r="A3" s="32"/>
       <c r="B3" t="s">
         <v>53</v>
       </c>
@@ -2567,7 +2568,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="16"/>
+      <c r="A4" s="32"/>
       <c r="B4" t="s">
         <v>75</v>
       </c>
@@ -2576,7 +2577,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="33" t="s">
         <v>77</v>
       </c>
       <c r="B5" t="s">
@@ -2587,7 +2588,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="17"/>
+      <c r="A6" s="33"/>
       <c r="B6" t="s">
         <v>80</v>
       </c>
@@ -2596,7 +2597,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="17"/>
+      <c r="A7" s="33"/>
       <c r="B7" t="s">
         <v>82</v>
       </c>
@@ -2605,7 +2606,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="17"/>
+      <c r="A8" s="33"/>
       <c r="B8" t="s">
         <v>84</v>
       </c>
@@ -2614,7 +2615,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="17"/>
+      <c r="A9" s="33"/>
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -2623,7 +2624,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="34" t="s">
         <v>87</v>
       </c>
       <c r="B10" t="s">
@@ -2634,7 +2635,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="18"/>
+      <c r="A11" s="34"/>
       <c r="B11" t="s">
         <v>89</v>
       </c>
@@ -2643,7 +2644,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="35" t="s">
         <v>91</v>
       </c>
       <c r="B12" t="s">
@@ -2654,7 +2655,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="19"/>
+      <c r="A13" s="35"/>
       <c r="B13" t="s">
         <v>93</v>
       </c>
@@ -2663,7 +2664,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="19"/>
+      <c r="A14" s="35"/>
       <c r="B14" t="s">
         <v>95</v>
       </c>

--- a/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="11_07EE13C193757A3225BDE5FB35085310783B1F5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F29A52D8-D549-489C-B0CD-5C06E0733BF3}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="11_07EE13C193757A3225BDE5FB35085310783B1F5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F365C191-8F26-4C11-ADF4-D89546ED2530}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="122">
   <si>
     <t>Project ID</t>
   </si>
@@ -107,7 +107,7 @@
     <t>Urban Transport</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=5304</t>
   </si>
   <si>
     <t>Other</t>
@@ -119,34 +119,43 @@
     <t>These are all from prodoc</t>
   </si>
   <si>
+    <t>GEF</t>
+  </si>
+  <si>
     <t>VF</t>
   </si>
   <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of daily users of new transport options using low carbon transport systems </t>
+  </si>
+  <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t>Cumulative investment in new low carbon vehicle projects by EOP (USD)</t>
+  </si>
+  <si>
+    <t>DREAMS</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=5194</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
+    <t>Cumulative direct project CO2 emission reductions from RE development by end-of-project (EOP), tonnes CO2</t>
+  </si>
+  <si>
+    <t>Direct GHG avoidance calculated according the GEF Manual for GHG Reductions from RE Projects</t>
+  </si>
+  <si>
     <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Transportation and E-mobility Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of daily users of new transport options using low carbon transport systems </t>
-  </si>
-  <si>
-    <t>Market Intervention</t>
-  </si>
-  <si>
-    <t>Cumulative investment in new low carbon vehicle projects by EOP (USD)</t>
-  </si>
-  <si>
-    <t>DREAMS</t>
-  </si>
-  <si>
-    <t>GHG Emissions Reduction</t>
-  </si>
-  <si>
-    <t>Cumulative direct project CO2 emission reductions from RE development by end-of-project (EOP), tonnes CO2</t>
-  </si>
-  <si>
-    <t>Direct GHG avoidance calculated according the GEF Manual for GHG Reductions from RE Projects</t>
   </si>
   <si>
     <t>Percent share of RE in the power generation mix of the Philippines – based on installed capacity.</t>
@@ -268,6 +277,9 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
   </si>
   <si>
     <t>Transport Services</t>
@@ -424,7 +436,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +486,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -604,10 +624,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -696,6 +717,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -715,7 +739,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1158,7 +1183,7 @@
       <c r="B2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="32" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="15">
@@ -1174,17 +1199,19 @@
       <c r="H2" s="16">
         <v>222</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="15"/>
+      <c r="J2" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K2" s="15"/>
       <c r="L2" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="24"/>
       <c r="N2" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" s="24"/>
       <c r="P2" s="24"/>
@@ -1194,16 +1221,16 @@
       <c r="T2" s="24"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" spans="1:21" s="2" customFormat="1" ht="30.75">
+    <row r="3" spans="1:21" s="2" customFormat="1" ht="45.75">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
       <c r="E3" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="16">
         <v>6500</v>
@@ -1212,12 +1239,18 @@
         <f>(1.2^15)*6500</f>
         <v>100145.64023481136</v>
       </c>
-      <c r="I3" s="33"/>
-      <c r="J3" s="15"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K3" s="15"/>
-      <c r="L3" s="30"/>
+      <c r="L3" s="30" t="s">
+        <v>27</v>
+      </c>
       <c r="M3" s="24"/>
-      <c r="N3" s="31"/>
+      <c r="N3" s="31" t="s">
+        <v>28</v>
+      </c>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
@@ -1226,16 +1259,16 @@
       <c r="T3" s="24"/>
       <c r="U3" s="15"/>
     </row>
-    <row r="4" spans="1:21" s="2" customFormat="1" ht="30.75">
+    <row r="4" spans="1:21" s="2" customFormat="1" ht="45.75">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="16">
         <v>7500000</v>
@@ -1243,12 +1276,18 @@
       <c r="H4" s="16">
         <v>20000000</v>
       </c>
-      <c r="I4" s="34"/>
-      <c r="J4" s="15"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K4" s="15"/>
-      <c r="L4" s="30"/>
+      <c r="L4" s="30" t="s">
+        <v>27</v>
+      </c>
       <c r="M4" s="24"/>
-      <c r="N4" s="31"/>
+      <c r="N4" s="31" t="s">
+        <v>28</v>
+      </c>
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
       <c r="Q4" s="24"/>
@@ -1262,19 +1301,19 @@
         <v>5194</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="D5" s="15">
         <v>5200000</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="16">
         <v>0</v>
@@ -1283,16 +1322,18 @@
         <v>205000</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K5" s="15"/>
       <c r="L5" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
@@ -1309,7 +1350,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G6" s="19">
         <v>0.14399999999999999</v>
@@ -1318,16 +1359,18 @@
         <v>0.35</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K6" s="15"/>
       <c r="L6" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" s="24"/>
       <c r="N6" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
@@ -1343,35 +1386,37 @@
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7" s="15">
         <v>0</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K7" s="15"/>
       <c r="L7" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="24"/>
       <c r="N7" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
       <c r="Q7" s="24"/>
       <c r="R7" s="24"/>
       <c r="S7" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T7" s="24"/>
       <c r="U7" s="15"/>
@@ -1385,7 +1430,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" s="21">
         <v>0</v>
@@ -1394,30 +1439,32 @@
         <v>8</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="21"/>
+        <v>47</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O8" s="24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P8" s="24"/>
       <c r="Q8" s="24" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S8" s="15"/>
       <c r="T8" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U8" s="15"/>
     </row>
@@ -1428,7 +1475,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" s="15">
         <v>0</v>
@@ -1437,16 +1484,18 @@
         <v>12</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="15"/>
+        <v>52</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K9" s="15"/>
       <c r="L9" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" s="24"/>
       <c r="N9" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
@@ -1462,10 +1511,10 @@
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="15">
         <v>9</v>
@@ -1474,16 +1523,18 @@
         <v>50</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K10" s="15"/>
       <c r="L10" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
@@ -1500,23 +1551,25 @@
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
       <c r="F11" s="18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" s="15">
         <v>0</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="15"/>
+        <v>57</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K11" s="15"/>
       <c r="L11" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
@@ -1533,23 +1586,25 @@
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G12" s="15">
         <v>0</v>
       </c>
       <c r="H12" s="15"/>
       <c r="I12" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="15"/>
+        <v>59</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K12" s="15"/>
       <c r="L12" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M12" s="24"/>
       <c r="N12" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
@@ -1566,23 +1621,25 @@
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" s="15">
         <v>0</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="15"/>
+        <v>61</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K13" s="15"/>
       <c r="L13" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" s="24"/>
       <c r="N13" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
@@ -1598,10 +1655,10 @@
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G14" s="15">
         <v>0</v>
@@ -1610,23 +1667,25 @@
         <v>10</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="15"/>
+        <v>64</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K14" s="15"/>
       <c r="L14" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T14" s="24"/>
       <c r="U14" s="15"/>
@@ -1638,7 +1697,7 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" s="15">
         <v>0</v>
@@ -1647,16 +1706,18 @@
         <v>15</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="15"/>
+        <v>64</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K15" s="15"/>
       <c r="L15" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" s="24"/>
       <c r="N15" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
@@ -1672,10 +1733,10 @@
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G16" s="15">
         <v>0</v>
@@ -1684,23 +1745,25 @@
         <v>15</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="15"/>
+        <v>67</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K16" s="15"/>
       <c r="L16" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="24"/>
       <c r="N16" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T16" s="24"/>
       <c r="U16" s="15"/>
@@ -1712,7 +1775,7 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G17" s="15">
         <v>0</v>
@@ -1721,16 +1784,18 @@
         <v>3</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="15"/>
+        <v>69</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K17" s="15"/>
       <c r="L17" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M17" s="24"/>
       <c r="N17" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
@@ -1746,10 +1811,10 @@
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G18" s="15">
         <v>0</v>
@@ -1758,16 +1823,18 @@
         <v>10</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K18" s="15"/>
       <c r="L18" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M18" s="24"/>
       <c r="N18" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
@@ -1783,10 +1850,10 @@
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G19" s="15">
         <v>0</v>
@@ -1795,23 +1862,25 @@
         <v>5</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19" s="15"/>
+        <v>74</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K19" s="15"/>
       <c r="L19" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M19" s="24"/>
       <c r="N19" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O19" s="24"/>
       <c r="P19" s="24"/>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T19" s="24"/>
       <c r="U19" s="15"/>
@@ -1822,10 +1891,10 @@
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G20" s="15">
         <v>0</v>
@@ -1834,23 +1903,25 @@
         <v>75</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="15"/>
+        <v>76</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="K20" s="15"/>
       <c r="L20" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M20" s="24"/>
       <c r="N20" s="31" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="O20" s="24"/>
       <c r="P20" s="24"/>
       <c r="Q20" s="24"/>
       <c r="R20" s="24"/>
       <c r="S20" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T20" s="24"/>
       <c r="U20" s="15"/>
@@ -1888,6 +1959,10 @@
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{6F1F70C9-F0B9-4D44-AFE4-BF9AC35F5C63}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{92731A32-FE77-4378-B0D5-FB0B7CE67387}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <extLst>
@@ -1953,10 +2028,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1">
@@ -1967,13 +2042,13 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2">
         <v>2639726</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1982,10 +2057,10 @@
       </c>
       <c r="I2" s="3"/>
       <c r="L2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" ht="30.75">
@@ -1993,19 +2068,19 @@
         <v>5194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D3" s="2">
         <v>5200000</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -2014,18 +2089,18 @@
         <v>205000</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" ht="30.75">
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6">
         <v>0.14399999999999999</v>
@@ -2034,34 +2109,34 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" ht="30.75">
@@ -2069,7 +2144,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -2078,13 +2153,13 @@
         <v>8</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" ht="30.75">
@@ -2092,7 +2167,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -2101,21 +2176,21 @@
         <v>12</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2">
         <v>9</v>
@@ -2124,72 +2199,72 @@
         <v>50</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E9" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" s="11"/>
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" ht="60.75">
       <c r="E10" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" s="11"/>
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" s="11"/>
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -2198,18 +2273,18 @@
         <v>10</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E13" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
@@ -2218,18 +2293,18 @@
         <v>15</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" ht="30.75">
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
@@ -2238,10 +2313,10 @@
         <v>15</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" ht="76.5">
@@ -2249,7 +2324,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -2258,18 +2333,18 @@
         <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" ht="45.75">
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -2278,18 +2353,18 @@
         <v>10</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="5:12" s="2" customFormat="1" ht="137.25">
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -2298,18 +2373,18 @@
         <v>5</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="5:12" s="2" customFormat="1" ht="121.5">
       <c r="E18" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -2318,10 +2393,10 @@
         <v>75</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2473,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2">
         <v>2639726</v>
@@ -2416,10 +2491,10 @@
         <v>5194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D3" s="2">
         <v>5200000</v>
@@ -2428,7 +2503,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -2437,7 +2512,7 @@
         <v>205</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="30.75">
@@ -2445,16 +2520,16 @@
         <v>5194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2">
         <v>5200000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6">
         <v>0.14399999999999999</v>
@@ -2463,7 +2538,7 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2471,25 +2546,25 @@
         <v>5194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2">
         <v>5200000</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="30.75">
@@ -2497,7 +2572,7 @@
         <v>5194</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2">
         <v>5200000</v>
@@ -2506,7 +2581,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -2515,7 +2590,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="30.75">
@@ -2523,7 +2598,7 @@
         <v>5194</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2">
         <v>5200000</v>
@@ -2532,7 +2607,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -2541,7 +2616,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2549,16 +2624,16 @@
         <v>5194</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2">
         <v>5200000</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2">
         <v>9</v>
@@ -2567,7 +2642,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2575,16 +2650,16 @@
         <v>5194</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2">
         <v>5200000</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -2593,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="60.75">
@@ -2601,16 +2676,16 @@
         <v>5194</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2">
         <v>5200000</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -2619,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2627,16 +2702,16 @@
         <v>5194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2">
         <v>5200000</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -2645,7 +2720,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2653,7 +2728,7 @@
         <v>5194</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2">
         <v>5200000</v>
@@ -2662,7 +2737,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -2671,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2679,7 +2754,7 @@
         <v>5194</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2">
         <v>5200000</v>
@@ -2688,7 +2763,7 @@
         <v>23</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
@@ -2697,7 +2772,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="30.75">
@@ -2705,16 +2780,16 @@
         <v>5194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2">
         <v>5200000</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
@@ -2723,7 +2798,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="76.5">
@@ -2731,16 +2806,16 @@
         <v>5194</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2">
         <v>5200000</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -2749,7 +2824,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="45.75">
@@ -2757,16 +2832,16 @@
         <v>5194</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2">
         <v>5200000</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
@@ -2775,7 +2850,7 @@
         <v>10</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="137.25">
@@ -2783,16 +2858,16 @@
         <v>5194</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
         <v>5200000</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -2801,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="121.5">
@@ -2809,16 +2884,16 @@
         <v>5194</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2">
         <v>5200000</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -2827,7 +2902,7 @@
         <v>75</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2865,171 +2940,171 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="35" t="s">
-        <v>38</v>
+      <c r="A2" s="36" t="s">
+        <v>41</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="35" t="s">
-        <v>59</v>
+      <c r="A3" s="36" t="s">
+        <v>62</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="36" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>104</v>
+      <c r="B13" s="37" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>106</v>
+      <c r="A14" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>107</v>
+      <c r="A15" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>109</v>
+      <c r="A16" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="35" t="s">
-        <v>67</v>
+      <c r="A17" s="36" t="s">
+        <v>70</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>112</v>
+      <c r="A18" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>113</v>
+      <c r="A19" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>115</v>
+      <c r="A20" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="37" t="s">
-        <v>116</v>
+      <c r="B21" s="38" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="36" t="s">
-        <v>117</v>
+      <c r="B22" s="37" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3038,28 +3113,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3084,6 +3139,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3163,6 +3219,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3306,14 +3367,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9D103A4-8629-4334-9C7A-F7808F718D20}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{194DB693-C70A-42D6-B9B1-88F44F16E2A3}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1195EE3F-E7E6-4651-AAE5-31740C95F8AD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA717A6-D587-45C4-A85F-16172A46C019}"/>
 </file>
--- a/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Philippines - Energy Projects.xlsx
@@ -228,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -344,9 +344,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -428,6 +425,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -983,7 +1000,11 @@
       <c r="F3" s="15" t="n"/>
       <c r="G3" s="15" t="n"/>
       <c r="H3" s="15" t="n"/>
-      <c r="I3" s="41" t="n"/>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Transportation and E-mobility Services</t>
+        </is>
+      </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Number of daily users of new transport options using low carbon transport systems </t>
@@ -992,11 +1013,9 @@
       <c r="K3" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="L3" s="16">
-        <f>(1.2^15)*6500</f>
-        <v/>
-      </c>
-      <c r="M3" s="41" t="n"/>
+      <c r="L3" s="16" t="n">
+        <v>100145.6402348114</v>
+      </c>
       <c r="N3" s="15" t="inlineStr">
         <is>
           <t>GEF</t>
@@ -1026,7 +1045,11 @@
       <c r="F4" s="15" t="n"/>
       <c r="G4" s="15" t="n"/>
       <c r="H4" s="15" t="n"/>
-      <c r="I4" s="42" t="n"/>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Market Intervention</t>
+        </is>
+      </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Cumulative investment in new low carbon vehicle projects by EOP (USD)</t>
@@ -1038,7 +1061,6 @@
       <c r="L4" s="16" t="n">
         <v>20000000</v>
       </c>
-      <c r="M4" s="42" t="n"/>
       <c r="N4" s="15" t="inlineStr">
         <is>
           <t>GEF</t>
@@ -1078,15 +1100,10 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="39" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="39" t="n"/>
-      <c r="M5" s="43" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
       <c r="N5" s="15" t="n"/>
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="24" t="n"/>
@@ -1921,10 +1938,7 @@
       <c r="X21" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I2:I4"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="N2:N20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
@@ -1955,18 +1969,13 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3245,288 +3254,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="45" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="42" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="42" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
